--- a/StructureDefinition-RevisionshistorikTA.xlsx
+++ b/StructureDefinition-RevisionshistorikTA.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-RevisionshistorikTA.xlsx
+++ b/StructureDefinition-RevisionshistorikTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -254,16 +254,25 @@
     <t>Source attribute: Version 4.0; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Ny informationsspecifikation för laboratoriesvar fastställd.</t>
+  </si>
+  <si>
     <t>RevisionshistorikTA.Version401</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0.1; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Uppdaterat samtliga urval.</t>
+  </si>
+  <si>
     <t>RevisionshistorikTA.Version402</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0.2; type could not be resolved from source model</t>
+  </si>
+  <si>
+    <t>Uppdaterad med exempel för resistensbestämning.</t>
   </si>
 </sst>
 </file>
@@ -849,7 +858,7 @@
         <v>78</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -917,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -946,10 +955,10 @@
         <v>77</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1000,7 +1009,7 @@
         <v>19</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>71</v>
@@ -1017,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1046,10 +1055,10 @@
         <v>77</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1100,7 +1109,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>71</v>
